--- a/analysis/econometrics_outputs/sdid/Graficos/contracts/sdid_eventstudy_cosine_nearest_top_vs_bottom.xlsx
+++ b/analysis/econometrics_outputs/sdid/Graficos/contracts/sdid_eventstudy_cosine_nearest_top_vs_bottom.xlsx
@@ -507,13 +507,13 @@
         <v>2876.168</v>
       </c>
       <c r="I2" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J2" t="n">
-        <v>-327.1927657168</v>
+        <v>-470.4625067465572</v>
       </c>
       <c r="K2" t="n">
-        <v>550.7989592651867</v>
+        <v>694.0687002949439</v>
       </c>
     </row>
     <row r="3">
@@ -550,13 +550,13 @@
         <v>2575.836</v>
       </c>
       <c r="I3" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J3" t="n">
-        <v>-103.9333463619615</v>
+        <v>-247.2030873917188</v>
       </c>
       <c r="K3" t="n">
-        <v>774.0583786200251</v>
+        <v>917.3281196497824</v>
       </c>
     </row>
     <row r="4">
@@ -593,13 +593,13 @@
         <v>3112.868</v>
       </c>
       <c r="I4" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J4" t="n">
-        <v>-328.9492173297029</v>
+        <v>-472.2189583594602</v>
       </c>
       <c r="K4" t="n">
-        <v>549.0425076522837</v>
+        <v>692.3122486820409</v>
       </c>
     </row>
     <row r="5">
@@ -636,13 +636,13 @@
         <v>3040.771999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J5" t="n">
-        <v>-292.70805603938</v>
+        <v>-435.9777970691373</v>
       </c>
       <c r="K5" t="n">
-        <v>585.2836689426066</v>
+        <v>728.5534099723639</v>
       </c>
     </row>
     <row r="6">
@@ -679,13 +679,13 @@
         <v>3465.04</v>
       </c>
       <c r="I6" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J6" t="n">
-        <v>-612.4921850716386</v>
+        <v>-755.7619261013958</v>
       </c>
       <c r="K6" t="n">
-        <v>265.4995399103481</v>
+        <v>408.7692809401053</v>
       </c>
     </row>
     <row r="7">
@@ -722,13 +722,13 @@
         <v>4192.092000000002</v>
       </c>
       <c r="I7" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J7" t="n">
-        <v>-900.6006366845442</v>
+        <v>-1043.870377714301</v>
       </c>
       <c r="K7" t="n">
-        <v>-22.60891170255752</v>
+        <v>120.6608293271997</v>
       </c>
     </row>
     <row r="8">
@@ -765,13 +765,13 @@
         <v>4540.752</v>
       </c>
       <c r="I8" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J8" t="n">
-        <v>-1290.470314103897</v>
+        <v>-1433.740055133655</v>
       </c>
       <c r="K8" t="n">
-        <v>-412.4785891219107</v>
+        <v>-269.2088480921534</v>
       </c>
     </row>
     <row r="9">
@@ -808,13 +808,13 @@
         <v>3502.096</v>
       </c>
       <c r="I9" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J9" t="n">
-        <v>-900.5239915232515</v>
+        <v>-1043.793732553009</v>
       </c>
       <c r="K9" t="n">
-        <v>-22.5322665412649</v>
+        <v>120.7374744884924</v>
       </c>
     </row>
     <row r="10">
@@ -851,13 +851,13 @@
         <v>4373.424</v>
       </c>
       <c r="I10" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J10" t="n">
-        <v>-1104.319733458735</v>
+        <v>-1247.589474488493</v>
       </c>
       <c r="K10" t="n">
-        <v>-226.3280084767488</v>
+        <v>-83.05826744699152</v>
       </c>
     </row>
     <row r="11">
@@ -894,13 +894,13 @@
         <v>4349.632000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J11" t="n">
-        <v>-1092.043862490994</v>
+        <v>-1235.313603520751</v>
       </c>
       <c r="K11" t="n">
-        <v>-214.0521375090074</v>
+        <v>-70.78239647925011</v>
       </c>
     </row>
     <row r="12">
@@ -937,13 +937,13 @@
         <v>4614.956</v>
       </c>
       <c r="I12" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J12" t="n">
-        <v>-1207.738830232929</v>
+        <v>-1351.008571262686</v>
       </c>
       <c r="K12" t="n">
-        <v>-329.7471052509426</v>
+        <v>-186.4773642211853</v>
       </c>
     </row>
     <row r="13">
@@ -980,13 +980,13 @@
         <v>3744.3</v>
       </c>
       <c r="I13" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J13" t="n">
-        <v>-740.5344431361544</v>
+        <v>-883.8041841659117</v>
       </c>
       <c r="K13" t="n">
-        <v>137.4572818458322</v>
+        <v>280.7270228755895</v>
       </c>
     </row>
     <row r="14">
@@ -1023,13 +1023,13 @@
         <v>3529.02</v>
       </c>
       <c r="I14" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J14" t="n">
-        <v>-572.5447657167998</v>
+        <v>-715.8145067465571</v>
       </c>
       <c r="K14" t="n">
-        <v>305.4469592651868</v>
+        <v>448.7167002949441</v>
       </c>
     </row>
     <row r="15">
@@ -1066,13 +1066,13 @@
         <v>3173.040000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J15" t="n">
-        <v>-268.6212173297039</v>
+        <v>-411.8909583594611</v>
       </c>
       <c r="K15" t="n">
-        <v>609.3705076522828</v>
+        <v>752.64024868204</v>
       </c>
     </row>
     <row r="16">
@@ -1109,13 +1109,13 @@
         <v>3675.011999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J16" t="n">
-        <v>-357.3593463619605</v>
+        <v>-500.6290873917178</v>
       </c>
       <c r="K16" t="n">
-        <v>520.6323786200261</v>
+        <v>663.9021196497833</v>
       </c>
     </row>
     <row r="17">
@@ -1152,13 +1152,13 @@
         <v>3329.963999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J17" t="n">
-        <v>-346.3274753942188</v>
+        <v>-489.5972164239761</v>
       </c>
       <c r="K17" t="n">
-        <v>531.6642495877678</v>
+        <v>674.9339906175251</v>
       </c>
     </row>
     <row r="18">
@@ -1195,13 +1195,13 @@
         <v>3749.080000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J18" t="n">
-        <v>-615.0241205555104</v>
+        <v>-758.2938615852677</v>
       </c>
       <c r="K18" t="n">
-        <v>262.9676044264762</v>
+        <v>406.2373454562335</v>
       </c>
     </row>
     <row r="19">
@@ -1238,13 +1238,13 @@
         <v>4141.900000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J19" t="n">
-        <v>-727.7231528135745</v>
+        <v>-870.9928938433318</v>
       </c>
       <c r="K19" t="n">
-        <v>150.2685721684121</v>
+        <v>293.5383131981694</v>
       </c>
     </row>
     <row r="20">
@@ -1281,13 +1281,13 @@
         <v>4026.228</v>
       </c>
       <c r="I20" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J20" t="n">
-        <v>-733.1882495877677</v>
+        <v>-876.457990617525</v>
       </c>
       <c r="K20" t="n">
-        <v>144.8034753942189</v>
+        <v>288.0732164239762</v>
       </c>
     </row>
     <row r="21">
@@ -1324,13 +1324,13 @@
         <v>3123.584</v>
       </c>
       <c r="I21" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J21" t="n">
-        <v>-438.9958624909933</v>
+        <v>-582.2656035207506</v>
       </c>
       <c r="K21" t="n">
-        <v>438.9958624909933</v>
+        <v>582.2656035207506</v>
       </c>
     </row>
     <row r="22">
@@ -1367,13 +1367,13 @@
         <v>3622.688000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J22" t="n">
-        <v>-367.261152813575</v>
+        <v>-510.5308938433323</v>
       </c>
       <c r="K22" t="n">
-        <v>510.7305721684116</v>
+        <v>654.0003131981689</v>
       </c>
     </row>
     <row r="23">
@@ -1410,13 +1410,13 @@
         <v>3379.656</v>
       </c>
       <c r="I23" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J23" t="n">
-        <v>-269.3178624909939</v>
+        <v>-412.5876035207511</v>
       </c>
       <c r="K23" t="n">
-        <v>608.6738624909927</v>
+        <v>751.94360352075</v>
       </c>
     </row>
     <row r="24">
@@ -1453,13 +1453,13 @@
         <v>3065.792</v>
       </c>
       <c r="I24" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J24" t="n">
-        <v>2.328395573522698</v>
+        <v>-140.9413454562346</v>
       </c>
       <c r="K24" t="n">
-        <v>880.3201205555093</v>
+        <v>1023.589861585267</v>
       </c>
     </row>
     <row r="25">
@@ -1496,13 +1496,13 @@
         <v>2547.760000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J25" t="n">
-        <v>124.1587826702959</v>
+        <v>-19.11095835946139</v>
       </c>
       <c r="K25" t="n">
-        <v>1002.150507652282</v>
+        <v>1145.42024868204</v>
       </c>
     </row>
     <row r="26">
@@ -1539,13 +1539,13 @@
         <v>2561.980000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J26" t="n">
-        <v>111.7452342831992</v>
+        <v>-31.52450674655802</v>
       </c>
       <c r="K26" t="n">
-        <v>989.7369592651859</v>
+        <v>1133.006700294943</v>
       </c>
     </row>
     <row r="27">
@@ -1582,13 +1582,13 @@
         <v>2339.748000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J27" t="n">
-        <v>271.5417504122319</v>
+        <v>128.2720093824746</v>
       </c>
       <c r="K27" t="n">
-        <v>1149.533475394218</v>
+        <v>1292.803216423976</v>
       </c>
     </row>
     <row r="28">
@@ -1625,13 +1625,13 @@
         <v>2912.652</v>
       </c>
       <c r="I28" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J28" t="n">
-        <v>-42.7332173297026</v>
+        <v>-186.0029583594599</v>
       </c>
       <c r="K28" t="n">
-        <v>835.258507652284</v>
+        <v>978.5282486820413</v>
       </c>
     </row>
     <row r="29">
@@ -1668,13 +1668,13 @@
         <v>2584.456</v>
       </c>
       <c r="I29" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J29" t="n">
-        <v>36.99504073481296</v>
+        <v>-106.2747002949443</v>
       </c>
       <c r="K29" t="n">
-        <v>914.9867657167996</v>
+        <v>1058.256506746557</v>
       </c>
     </row>
     <row r="30">
@@ -1711,13 +1711,13 @@
         <v>3124.34</v>
       </c>
       <c r="I30" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J30" t="n">
-        <v>-227.0502495877678</v>
+        <v>-370.319990617525</v>
       </c>
       <c r="K30" t="n">
-        <v>650.9414753942189</v>
+        <v>794.2112164239761</v>
       </c>
     </row>
     <row r="31">
@@ -1754,13 +1754,13 @@
         <v>3432.599999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J31" t="n">
-        <v>-270.8667012006698</v>
+        <v>-414.1364422304271</v>
       </c>
       <c r="K31" t="n">
-        <v>607.1250237813168</v>
+        <v>750.3947648110741</v>
       </c>
     </row>
     <row r="32">
@@ -1797,13 +1797,13 @@
         <v>3407.46</v>
       </c>
       <c r="I32" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J32" t="n">
-        <v>-326.8315399103479</v>
+        <v>-470.1012809401052</v>
       </c>
       <c r="K32" t="n">
-        <v>551.1601850716387</v>
+        <v>694.4299261013959</v>
       </c>
     </row>
     <row r="33">
@@ -1840,13 +1840,13 @@
         <v>2615.7</v>
       </c>
       <c r="I33" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J33" t="n">
-        <v>-156.2570237813158</v>
+        <v>-299.526764811073</v>
       </c>
       <c r="K33" t="n">
-        <v>721.7347012006709</v>
+        <v>865.0044422304281</v>
       </c>
     </row>
     <row r="34">
@@ -1883,13 +1883,13 @@
         <v>3050.936</v>
       </c>
       <c r="I34" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J34" t="n">
-        <v>-114.5897979748646</v>
+        <v>-257.8595390046219</v>
       </c>
       <c r="K34" t="n">
-        <v>763.401927007122</v>
+        <v>906.6716680368793</v>
       </c>
     </row>
     <row r="35">
@@ -1926,13 +1926,13 @@
         <v>3112.400000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J35" t="n">
-        <v>-102.053797974865</v>
+        <v>-245.3235390046223</v>
       </c>
       <c r="K35" t="n">
-        <v>775.9379270071216</v>
+        <v>919.2076680368789</v>
       </c>
     </row>
     <row r="36">
@@ -1969,13 +1969,13 @@
         <v>2877.936000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J36" t="n">
-        <v>203.6440729928769</v>
+        <v>60.37433196311963</v>
       </c>
       <c r="K36" t="n">
-        <v>1081.635797974864</v>
+        <v>1224.905539004621</v>
       </c>
     </row>
     <row r="37">
@@ -2012,13 +2012,13 @@
         <v>2418.384</v>
       </c>
       <c r="I37" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J37" t="n">
-        <v>151.3251052509421</v>
+        <v>8.055364221184846</v>
       </c>
       <c r="K37" t="n">
-        <v>1029.316830232929</v>
+        <v>1172.586571262686</v>
       </c>
     </row>
     <row r="38">
@@ -2055,13 +2055,13 @@
         <v>2619.036000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J38" t="n">
-        <v>95.43116976707063</v>
+        <v>-47.83857126268663</v>
       </c>
       <c r="K38" t="n">
-        <v>973.4228947490573</v>
+        <v>1116.692635778815</v>
       </c>
     </row>
     <row r="39">
@@ -2098,13 +2098,13 @@
         <v>2468.963999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J39" t="n">
-        <v>203.6322020251361</v>
+        <v>60.3624609953788</v>
       </c>
       <c r="K39" t="n">
-        <v>1081.623927007123</v>
+        <v>1224.89366803688</v>
       </c>
     </row>
     <row r="40">
@@ -2141,13 +2141,13 @@
         <v>2495.648</v>
       </c>
       <c r="I40" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J40" t="n">
-        <v>162.9562665412644</v>
+        <v>19.68652551150717</v>
       </c>
       <c r="K40" t="n">
-        <v>1040.947991523251</v>
+        <v>1184.217732553008</v>
       </c>
     </row>
     <row r="41">
@@ -2184,13 +2184,13 @@
         <v>2823.384</v>
       </c>
       <c r="I41" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J41" t="n">
-        <v>-21.00553991034792</v>
+        <v>-164.2752809401052</v>
       </c>
       <c r="K41" t="n">
-        <v>856.9861850716387</v>
+        <v>1000.255926101396</v>
       </c>
     </row>
     <row r="42">
@@ -2227,13 +2227,13 @@
         <v>3010.348000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J42" t="n">
-        <v>-174.4856689426073</v>
+        <v>-317.7554099723645</v>
       </c>
       <c r="K42" t="n">
-        <v>703.5060560393794</v>
+        <v>846.7757970691366</v>
       </c>
     </row>
     <row r="43">
@@ -2270,13 +2270,13 @@
         <v>3180.672</v>
       </c>
       <c r="I43" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J43" t="n">
-        <v>-121.5677334587359</v>
+        <v>-264.8374744884932</v>
       </c>
       <c r="K43" t="n">
-        <v>756.4239915232507</v>
+        <v>899.693732553008</v>
       </c>
     </row>
     <row r="44">
@@ -2313,13 +2313,13 @@
         <v>3656.06</v>
       </c>
       <c r="I44" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J44" t="n">
-        <v>-427.8831528135744</v>
+        <v>-571.1528938433316</v>
       </c>
       <c r="K44" t="n">
-        <v>450.1085721684123</v>
+        <v>593.3783131981695</v>
       </c>
     </row>
     <row r="45">
@@ -2356,13 +2356,13 @@
         <v>2493.703999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J45" t="n">
-        <v>-62.36586249099275</v>
+        <v>-205.63560352075</v>
       </c>
       <c r="K45" t="n">
-        <v>815.6258624909939</v>
+        <v>958.8956035207511</v>
       </c>
     </row>
     <row r="46">
@@ -2399,13 +2399,13 @@
         <v>3142.816</v>
       </c>
       <c r="I46" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J46" t="n">
-        <v>-167.9697979748643</v>
+        <v>-311.2395390046215</v>
       </c>
       <c r="K46" t="n">
-        <v>710.0219270071224</v>
+        <v>853.2916680368796</v>
       </c>
     </row>
     <row r="47">
@@ -2442,13 +2442,13 @@
         <v>3434.048</v>
       </c>
       <c r="I47" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J47" t="n">
-        <v>-318.3792173297032</v>
+        <v>-461.6489583594605</v>
       </c>
       <c r="K47" t="n">
-        <v>559.6125076522834</v>
+        <v>702.8822486820407</v>
       </c>
     </row>
     <row r="48">
@@ -2485,13 +2485,13 @@
         <v>2786.708</v>
       </c>
       <c r="I48" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J48" t="n">
-        <v>63.29142783158716</v>
+        <v>-79.9783131981701</v>
       </c>
       <c r="K48" t="n">
-        <v>941.2831528135738</v>
+        <v>1084.552893843331</v>
       </c>
     </row>
     <row r="49">
@@ -2528,13 +2528,13 @@
         <v>2530.692</v>
       </c>
       <c r="I49" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J49" t="n">
-        <v>118.4445246057807</v>
+        <v>-24.8252164239766</v>
       </c>
       <c r="K49" t="n">
-        <v>996.4362495877673</v>
+        <v>1139.705990617525</v>
       </c>
     </row>
     <row r="50">
@@ -2571,13 +2571,13 @@
         <v>2639.432</v>
       </c>
       <c r="I50" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J50" t="n">
-        <v>72.1642020251353</v>
+        <v>-71.10553900462196</v>
       </c>
       <c r="K50" t="n">
-        <v>950.1559270071219</v>
+        <v>1093.425668036879</v>
       </c>
     </row>
     <row r="51">
@@ -2614,13 +2614,13 @@
         <v>2381.971999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J51" t="n">
-        <v>218.8742020251362</v>
+        <v>75.60446099537899</v>
       </c>
       <c r="K51" t="n">
-        <v>1096.865927007123</v>
+        <v>1240.13566803688</v>
       </c>
     </row>
     <row r="52">
@@ -2657,13 +2657,13 @@
         <v>2602.26</v>
       </c>
       <c r="I52" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J52" t="n">
-        <v>145.6829762186838</v>
+        <v>2.413235188926592</v>
       </c>
       <c r="K52" t="n">
-        <v>1023.67470120067</v>
+        <v>1166.944442230428</v>
       </c>
     </row>
     <row r="53">
@@ -2700,13 +2700,13 @@
         <v>2581.472</v>
       </c>
       <c r="I53" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J53" t="n">
-        <v>81.64033105739384</v>
+        <v>-61.62940997236342</v>
       </c>
       <c r="K53" t="n">
-        <v>959.6320560393805</v>
+        <v>1102.901797069138</v>
       </c>
     </row>
     <row r="54">
@@ -2743,13 +2743,13 @@
         <v>3022.759999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J54" t="n">
-        <v>-194.7202495877665</v>
+        <v>-337.9899906175237</v>
       </c>
       <c r="K54" t="n">
-        <v>683.2714753942201</v>
+        <v>826.5412164239774</v>
       </c>
     </row>
     <row r="55">
@@ -2786,13 +2786,13 @@
         <v>3466.591999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J55" t="n">
-        <v>-283.1651528135727</v>
+        <v>-426.43489384333</v>
       </c>
       <c r="K55" t="n">
-        <v>594.8265721684139</v>
+        <v>738.0963131981712</v>
       </c>
     </row>
     <row r="56">
@@ -2829,13 +2829,13 @@
         <v>3875.528</v>
       </c>
       <c r="I56" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J56" t="n">
-        <v>-623.5527657168001</v>
+        <v>-766.8225067465573</v>
       </c>
       <c r="K56" t="n">
-        <v>254.4389592651866</v>
+        <v>397.7087002949438</v>
       </c>
     </row>
     <row r="57">
@@ -2872,13 +2872,13 @@
         <v>2531.836</v>
       </c>
       <c r="I57" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J57" t="n">
-        <v>-104.8930237813157</v>
+        <v>-248.162764811073</v>
       </c>
       <c r="K57" t="n">
-        <v>773.0987012006709</v>
+        <v>916.3684422304282</v>
       </c>
     </row>
     <row r="58">
@@ -2915,13 +2915,13 @@
         <v>3418.488000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J58" t="n">
-        <v>-274.5450237813167</v>
+        <v>-417.8147648110739</v>
       </c>
       <c r="K58" t="n">
-        <v>603.44670120067</v>
+        <v>746.7164422304272</v>
       </c>
     </row>
     <row r="59">
@@ -2958,13 +2958,13 @@
         <v>3391.068</v>
       </c>
       <c r="I59" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J59" t="n">
-        <v>-277.8105076522835</v>
+        <v>-421.0802486820407</v>
       </c>
       <c r="K59" t="n">
-        <v>600.1812173297031</v>
+        <v>743.4509583594604</v>
       </c>
     </row>
     <row r="60">
@@ -3001,13 +3001,13 @@
         <v>2871.248000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J60" t="n">
-        <v>-0.8776044264778875</v>
+        <v>-144.1473454562351</v>
       </c>
       <c r="K60" t="n">
-        <v>877.1141205555087</v>
+        <v>1020.383861585266</v>
       </c>
     </row>
     <row r="61">
@@ -3044,13 +3044,13 @@
         <v>2701.280000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J61" t="n">
-        <v>17.93716976707049</v>
+        <v>-125.3325712626868</v>
       </c>
       <c r="K61" t="n">
-        <v>895.9288947490571</v>
+        <v>1039.198635778814</v>
       </c>
     </row>
     <row r="62">
@@ -3087,13 +3087,13 @@
         <v>2618.092000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J62" t="n">
-        <v>0.5525891219091363</v>
+        <v>-142.7171519078481</v>
       </c>
       <c r="K62" t="n">
-        <v>878.5443141038958</v>
+        <v>1021.814055133653</v>
       </c>
     </row>
     <row r="63">
@@ -3130,13 +3130,13 @@
         <v>2477.000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J63" t="n">
-        <v>130.4510407348122</v>
+        <v>-12.81870029494507</v>
       </c>
       <c r="K63" t="n">
-        <v>1008.442765716799</v>
+        <v>1151.712506746556</v>
       </c>
     </row>
     <row r="64">
@@ -3173,13 +3173,13 @@
         <v>2940.676</v>
       </c>
       <c r="I64" t="n">
-        <v>223.9774808627517</v>
+        <v>297.0742875105871</v>
       </c>
       <c r="J64" t="n">
-        <v>-93.93463668454217</v>
+        <v>-237.2043777142994</v>
       </c>
       <c r="K64" t="n">
-        <v>784.0570882974445</v>
+        <v>927.3268293272017</v>
       </c>
     </row>
   </sheetData>
